--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_15_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_15_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5485547F-871D-4C35-AAEB-77422F095A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9987E55-779D-4E30-AA8D-1D81CD1D1F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,37 +55,64 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT POLYCAB 31 Jul 2025 6900 CE</t>
-  </si>
-  <si>
-    <t>21-07-2025</t>
-  </si>
-  <si>
-    <t>OPT DALBHARAT 31 Jul 2025 2240 CE</t>
-  </si>
-  <si>
-    <t>OPT PATANJALI 31 Jul 2025 1900 PE</t>
-  </si>
-  <si>
-    <t>23-07-2025</t>
-  </si>
-  <si>
-    <t>OPT PAYTM 31 Jul 2025 1100 CE</t>
-  </si>
-  <si>
-    <t>24-07-2025</t>
-  </si>
-  <si>
-    <t>OPT BIOCON 31 Jul 2025 390 CE</t>
-  </si>
-  <si>
-    <t>OPT BAJAJFINSV 31 Jul 2025 2000 PE</t>
-  </si>
-  <si>
-    <t>25-07-2025</t>
-  </si>
-  <si>
-    <t>OPT APLAPOLLO 31 Jul 2025 1600 PE</t>
+    <t>OPT OFSS 28 Aug 2025 8800 CE</t>
+  </si>
+  <si>
+    <t>25-08-2025</t>
+  </si>
+  <si>
+    <t>OPT JSWSTEEL 28 Aug 2025 1050 CE</t>
+  </si>
+  <si>
+    <t>OPT TATAELXSI 28 Aug 2025 5600 CE</t>
+  </si>
+  <si>
+    <t>OPT ZYDUSLIFE 28 Aug 2025 1000 PE</t>
+  </si>
+  <si>
+    <t>26-08-2025</t>
+  </si>
+  <si>
+    <t>OPT DIVISLAB 28 Aug 2025 6000 PE</t>
+  </si>
+  <si>
+    <t>OPT COLPAL 30 Sep 2025 2260 PE</t>
+  </si>
+  <si>
+    <t>28-08-2025</t>
+  </si>
+  <si>
+    <t>OPT BIOCON 30 Sep 2025 360 PE</t>
+  </si>
+  <si>
+    <t>OPT ADANIPORTS 30 Sep 2025 1320 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 28 Aug 2025 24600 CE</t>
+  </si>
+  <si>
+    <t>OPT DLF 30 Sep 2025 740 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 28 Aug 2025 24700 PE</t>
+  </si>
+  <si>
+    <t>OPT HINDUNILVR 30 Sep 2025 2600 CE</t>
+  </si>
+  <si>
+    <t>29-08-2025</t>
+  </si>
+  <si>
+    <t>OPT DABUR 30 Sep 2025 500 CE</t>
+  </si>
+  <si>
+    <t>OPT RBLBANK 30 Sep 2025 260 CE</t>
+  </si>
+  <si>
+    <t>OPT VBL 30 Sep 2025 480 CE</t>
+  </si>
+  <si>
+    <t>OPT TRENT 30 Sep 2025 5300 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -438,10 +465,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.85546875" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -457,10 +484,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -469,10 +496,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -495,331 +522,754 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45859</v>
+        <v>45894</v>
       </c>
       <c r="D2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>190.9</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>23862.5</v>
+        <v>9675</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>211.55</v>
+        <v>150</v>
       </c>
       <c r="J2">
-        <v>26443.75</v>
+        <v>11250</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>2581.25</v>
+        <v>1575</v>
       </c>
       <c r="M2">
-        <v>95.51</v>
+        <v>67.62</v>
       </c>
       <c r="N2">
-        <v>2485.7399999999998</v>
+        <v>1507.38</v>
       </c>
       <c r="O2">
-        <v>2581.25</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45859</v>
+        <v>45894</v>
       </c>
       <c r="D3">
-        <v>325</v>
+        <v>675</v>
       </c>
       <c r="E3">
-        <v>72.95</v>
+        <v>14.7</v>
       </c>
       <c r="F3">
-        <v>23708.75</v>
+        <v>9922.5</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H3">
-        <v>325</v>
+        <v>675</v>
       </c>
       <c r="I3">
-        <v>83.1</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>27007.5</v>
+        <v>9450</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>3298.75</v>
+        <v>-472.5</v>
       </c>
       <c r="M3">
-        <v>95.37</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="N3">
-        <v>3203.38</v>
+        <v>-537.6</v>
       </c>
       <c r="O3">
-        <v>3298.75</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45861</v>
+        <v>45894</v>
       </c>
       <c r="D4">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>40.65</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>24390</v>
+        <v>7700</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>42.5</v>
+        <v>54</v>
       </c>
       <c r="J4">
-        <v>25500</v>
+        <v>5400</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1110</v>
+        <v>-2300</v>
       </c>
       <c r="M4">
-        <v>118.78</v>
+        <v>58.34</v>
       </c>
       <c r="N4">
-        <v>991.22</v>
+        <v>-2358.34</v>
       </c>
       <c r="O4">
-        <v>1110</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>226</v>
+        <v>291</v>
       </c>
       <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45895</v>
+      </c>
+      <c r="D5">
+        <v>900</v>
+      </c>
+      <c r="E5">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F5">
+        <v>9180</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1">
-        <v>45862</v>
-      </c>
-      <c r="D5">
-        <v>725</v>
-      </c>
-      <c r="E5">
-        <v>29.4</v>
-      </c>
-      <c r="F5">
-        <v>21315</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="H5">
-        <v>725</v>
+        <v>900</v>
       </c>
       <c r="I5">
-        <v>27.7</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>20082.5</v>
+        <v>13500</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-1232.5</v>
+        <v>4320</v>
       </c>
       <c r="M5">
-        <v>85.32</v>
+        <v>69.78</v>
       </c>
       <c r="N5">
-        <v>-1317.82</v>
+        <v>4250.22</v>
       </c>
       <c r="O5">
-        <v>1232.5</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>45862</v>
+        <v>45895</v>
       </c>
       <c r="D6">
-        <v>7500</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>14.7</v>
+        <v>7.5</v>
       </c>
       <c r="F6">
-        <v>110250</v>
+        <v>750</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>7500</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>13.65</v>
+        <v>9.5</v>
       </c>
       <c r="J6">
-        <v>102375</v>
+        <v>950</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-7875</v>
+        <v>200</v>
       </c>
       <c r="M6">
-        <v>289.07</v>
+        <v>48.86</v>
       </c>
       <c r="N6">
-        <v>-8164.07</v>
+        <v>151.13999999999999</v>
       </c>
       <c r="O6">
-        <v>7875</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D7">
+        <v>225</v>
+      </c>
+      <c r="E7">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>12375</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1">
-        <v>45863</v>
-      </c>
-      <c r="D7">
-        <v>500</v>
-      </c>
-      <c r="E7">
-        <v>67.8</v>
-      </c>
-      <c r="F7">
-        <v>33900</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H7">
-        <v>500</v>
+        <v>225</v>
       </c>
       <c r="I7">
-        <v>77.400000000000006</v>
+        <v>58.2</v>
       </c>
       <c r="J7">
-        <v>38700</v>
+        <v>13095</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>4800</v>
+        <v>720</v>
       </c>
       <c r="M7">
-        <v>117.53</v>
+        <v>71.38</v>
       </c>
       <c r="N7">
-        <v>4682.47</v>
+        <v>648.62</v>
       </c>
       <c r="O7">
-        <v>4800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D8">
+        <v>2500</v>
+      </c>
+      <c r="E8">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>30000</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8">
+        <v>2500</v>
+      </c>
+      <c r="I8">
+        <v>11.45</v>
+      </c>
+      <c r="J8">
+        <v>28625</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>-1375</v>
+      </c>
+      <c r="M8">
+        <v>101.3</v>
+      </c>
+      <c r="N8">
+        <v>-1476.3</v>
+      </c>
+      <c r="O8">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="1">
-        <v>45863</v>
-      </c>
-      <c r="D8">
-        <v>350</v>
-      </c>
-      <c r="E8">
-        <v>22.5</v>
-      </c>
-      <c r="F8">
-        <v>7875</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>350</v>
-      </c>
-      <c r="I8">
-        <v>22.7</v>
-      </c>
-      <c r="J8">
-        <v>7945</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
+      <c r="C9" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D9">
+        <v>475</v>
+      </c>
+      <c r="E9">
+        <v>46.6</v>
+      </c>
+      <c r="F9">
+        <v>22135</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>475</v>
+      </c>
+      <c r="I9">
+        <v>47.1</v>
+      </c>
+      <c r="J9">
+        <v>22372.5</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>237.5</v>
+      </c>
+      <c r="M9">
+        <v>88.94</v>
+      </c>
+      <c r="N9">
+        <v>148.56</v>
+      </c>
+      <c r="O9">
+        <v>237.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>189</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D10">
+        <v>75</v>
+      </c>
+      <c r="E10">
+        <v>83</v>
+      </c>
+      <c r="F10">
+        <v>6225</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10">
+        <v>75</v>
+      </c>
+      <c r="I10">
+        <v>63</v>
+      </c>
+      <c r="J10">
+        <v>4725</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>-1500</v>
+      </c>
+      <c r="M10">
+        <v>56.72</v>
+      </c>
+      <c r="N10">
+        <v>-1556.72</v>
+      </c>
+      <c r="O10">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D11">
+        <v>825</v>
+      </c>
+      <c r="E11">
+        <v>31.75</v>
+      </c>
+      <c r="F11">
+        <v>26193.75</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11">
+        <v>825</v>
+      </c>
+      <c r="I11">
+        <v>31.35</v>
+      </c>
+      <c r="J11">
+        <v>25863.75</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>-330</v>
+      </c>
+      <c r="M11">
+        <v>95.74</v>
+      </c>
+      <c r="N11">
+        <v>-425.74</v>
+      </c>
+      <c r="O11">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>193</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D12">
+        <v>75</v>
+      </c>
+      <c r="E12">
+        <v>85</v>
+      </c>
+      <c r="F12">
+        <v>6375</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12">
+        <v>75</v>
+      </c>
+      <c r="I12">
+        <v>83.75</v>
+      </c>
+      <c r="J12">
+        <v>6281.25</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>-93.75</v>
+      </c>
+      <c r="M12">
+        <v>58.99</v>
+      </c>
+      <c r="N12">
+        <v>-152.74</v>
+      </c>
+      <c r="O12">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D13">
+        <v>300</v>
+      </c>
+      <c r="E13">
+        <v>96.5</v>
+      </c>
+      <c r="F13">
+        <v>28950</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13">
+        <v>300</v>
+      </c>
+      <c r="I13">
+        <v>97.5</v>
+      </c>
+      <c r="J13">
+        <v>29250</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>300</v>
+      </c>
+      <c r="M13">
+        <v>101.79</v>
+      </c>
+      <c r="N13">
+        <v>198.21</v>
+      </c>
+      <c r="O13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>70</v>
       </c>
-      <c r="M8">
-        <v>62.04</v>
-      </c>
-      <c r="N8">
-        <v>7.96</v>
-      </c>
-      <c r="O8">
-        <v>70</v>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D14">
+        <v>1250</v>
+      </c>
+      <c r="E14">
+        <v>22.4</v>
+      </c>
+      <c r="F14">
+        <v>28000</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14">
+        <v>1250</v>
+      </c>
+      <c r="I14">
+        <v>24.25</v>
+      </c>
+      <c r="J14">
+        <v>30312.5</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>2312.5</v>
+      </c>
+      <c r="M14">
+        <v>102.87</v>
+      </c>
+      <c r="N14">
+        <v>2209.63</v>
+      </c>
+      <c r="O14">
+        <v>2312.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>243</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D15">
+        <v>3175</v>
+      </c>
+      <c r="E15">
+        <v>14.05</v>
+      </c>
+      <c r="F15">
+        <v>44608.75</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15">
+        <v>3175</v>
+      </c>
+      <c r="I15">
+        <v>14.7</v>
+      </c>
+      <c r="J15">
+        <v>46672.5</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>2063.75</v>
+      </c>
+      <c r="M15">
+        <v>134.22999999999999</v>
+      </c>
+      <c r="N15">
+        <v>1929.52</v>
+      </c>
+      <c r="O15">
+        <v>2063.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>285</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D16">
+        <v>1025</v>
+      </c>
+      <c r="E16">
+        <v>24</v>
+      </c>
+      <c r="F16">
+        <v>24600</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16">
+        <v>1025</v>
+      </c>
+      <c r="I16">
+        <v>22.45</v>
+      </c>
+      <c r="J16">
+        <v>23011.25</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>-1588.75</v>
+      </c>
+      <c r="M16">
+        <v>90.97</v>
+      </c>
+      <c r="N16">
+        <v>-1679.72</v>
+      </c>
+      <c r="O16">
+        <v>1588.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>282</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>238.9</v>
+      </c>
+      <c r="F17">
+        <v>23890</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>216</v>
+      </c>
+      <c r="J17">
+        <v>21600</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>-2290</v>
+      </c>
+      <c r="M17">
+        <v>88.65</v>
+      </c>
+      <c r="N17">
+        <v>-2378.65</v>
+      </c>
+      <c r="O17">
+        <v>2290</v>
       </c>
     </row>
   </sheetData>
